--- a/data/trans_orig/P6901-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P6901-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2007</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25077</t>
+          <t>25087</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37220</t>
+          <t>37054</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14988</t>
+          <t>15231</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25318</t>
+          <t>25361</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42972</t>
+          <t>43229</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58776</t>
+          <t>59344</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>83,04%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5624</t>
+          <t>5790</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17767</t>
+          <t>17757</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13631</t>
+          <t>13388</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12687</t>
+          <t>12119</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28491</t>
+          <t>28234</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>39,51%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50376</t>
+          <t>50622</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65061</t>
+          <t>65203</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23838</t>
+          <t>23266</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31685</t>
+          <t>31690</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>77975</t>
+          <t>78918</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>94586</t>
+          <t>94677</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,1%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7336</t>
+          <t>7194</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22021</t>
+          <t>21775</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>998</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8850</t>
+          <t>9422</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10498</t>
+          <t>10407</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>27109</t>
+          <t>26166</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>24,9%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22760</t>
+          <t>23496</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32856</t>
+          <t>32743</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10111</t>
+          <t>10936</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18866</t>
+          <t>18867</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36710</t>
+          <t>36556</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49792</t>
+          <t>49839</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,43%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>3872</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13855</t>
+          <t>13119</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2858</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11613</t>
+          <t>10788</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8547</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21629</t>
+          <t>21783</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,34%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35353</t>
+          <t>34632</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48909</t>
+          <t>48543</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12143</t>
+          <t>11665</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20066</t>
+          <t>20133</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>51,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50551</t>
+          <t>50459</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66817</t>
+          <t>66457</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,02%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9414</t>
+          <t>9780</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22970</t>
+          <t>23691</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t>2573</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10563</t>
+          <t>11041</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14212</t>
+          <t>14572</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>30478</t>
+          <t>30570</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,73%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11094</t>
+          <t>10913</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20141</t>
+          <t>19920</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>86,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>1948</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15541</t>
+          <t>14437</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25110</t>
+          <t>25359</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>84,74%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2813</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11860</t>
+          <t>12041</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>5022</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>4566</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14384</t>
+          <t>15488</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>51,76%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25594</t>
+          <t>25335</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36720</t>
+          <t>36757</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5825</t>
+          <t>6452</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13059</t>
+          <t>13055</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34909</t>
+          <t>35916</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>47984</t>
+          <t>47876</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,64%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5090</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16216</t>
+          <t>16475</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8269</t>
+          <t>7642</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7919</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20994</t>
+          <t>19987</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>35,75%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49456</t>
+          <t>50361</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67672</t>
+          <t>68020</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31667</t>
+          <t>30979</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40468</t>
+          <t>40750</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>72,74%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>85660</t>
+          <t>85455</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>106459</t>
+          <t>105920</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,25%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20776</t>
+          <t>20428</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>38087</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>2785</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11868</t>
+          <t>12556</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>25524</t>
+          <t>26063</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>46323</t>
+          <t>46528</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,25%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>76024</t>
+          <t>76337</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>92733</t>
+          <t>93230</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30832</t>
+          <t>30262</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>42705</t>
+          <t>42609</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>113145</t>
+          <t>112595</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>132588</t>
+          <t>133053</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>71,29%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,84%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>16182</t>
+          <t>15685</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>32891</t>
+          <t>32578</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>7177</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18954</t>
+          <t>19524</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>26113</t>
+          <t>25648</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>45556</t>
+          <t>46106</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>29,05%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>334550</t>
+          <t>335509</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>372165</t>
+          <t>372213</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>71,04%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>158216</t>
+          <t>158264</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>182869</t>
+          <t>183829</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>501482</t>
+          <t>501537</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>549421</t>
+          <t>546815</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>72,42%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>78,97%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>100140</t>
+          <t>100092</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>137755</t>
+          <t>136796</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>37252</t>
+          <t>36292</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>61905</t>
+          <t>61857</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>143006</t>
+          <t>145612</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>190945</t>
+          <t>190890</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2012</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2012 (tasa de respuesta: 98,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20249</t>
+          <t>20592</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32492</t>
+          <t>32905</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>52,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16243</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25360</t>
+          <t>25893</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40346</t>
+          <t>41596</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55624</t>
+          <t>55968</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,95%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7002</t>
+          <t>6589</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19245</t>
+          <t>18902</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2618</t>
+          <t>2085</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11194</t>
+          <t>11735</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11847</t>
+          <t>11503</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27125</t>
+          <t>25875</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>38,35%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43867</t>
+          <t>44674</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>53791</t>
+          <t>54591</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21207</t>
+          <t>21390</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31249</t>
+          <t>31285</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>69752</t>
+          <t>69894</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83804</t>
+          <t>83504</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>91,86%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12723</t>
+          <t>11916</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3066</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13108</t>
+          <t>12925</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7101</t>
+          <t>7401</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21153</t>
+          <t>21011</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,11%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18772</t>
+          <t>17837</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24396</t>
+          <t>24393</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,18%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9613</t>
+          <t>9525</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16933</t>
+          <t>16930</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30584</t>
+          <t>30532</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40403</t>
+          <t>40336</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,28%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>912</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>7468</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8322</t>
+          <t>8410</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2837</t>
+          <t>2904</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12656</t>
+          <t>12708</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,39%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33658</t>
+          <t>34253</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43778</t>
+          <t>44305</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16800</t>
+          <t>16782</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26548</t>
+          <t>26620</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55228</t>
+          <t>55382</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68231</t>
+          <t>68494</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,41%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3290</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13410</t>
+          <t>12815</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2987</t>
+          <t>2915</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12735</t>
+          <t>12753</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8372</t>
+          <t>8109</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21375</t>
+          <t>21221</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,7%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>7970</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15141</t>
+          <t>15148</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5845</t>
+          <t>5907</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -5478,7 +5478,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16410</t>
+          <t>17006</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25256</t>
+          <t>25687</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>92,3%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8063</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5816</t>
+          <t>5754</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2574</t>
+          <t>2143</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11420</t>
+          <t>10824</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>38,89%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25708</t>
+          <t>26105</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38028</t>
+          <t>37340</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10050</t>
+          <t>10032</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>38244</t>
+          <t>39064</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>51646</t>
+          <t>51403</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>66,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>87,77%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>6040</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17672</t>
+          <t>17275</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>5152</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6918</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20320</t>
+          <t>19500</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>33,3%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18785</t>
+          <t>19296</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34471</t>
+          <t>34052</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>62,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24942</t>
+          <t>25549</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38348</t>
+          <t>38996</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>48792</t>
+          <t>49081</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>69532</t>
+          <t>68403</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>67,85%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19959</t>
+          <t>20378</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>35645</t>
+          <t>35134</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8032</t>
+          <t>7384</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>21438</t>
+          <t>20831</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>31278</t>
+          <t>32407</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>52018</t>
+          <t>51729</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>51,31%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25437</t>
+          <t>25442</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37384</t>
+          <t>38017</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>56,38%</t>
+          <t>56,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19554</t>
+          <t>19672</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29542</t>
+          <t>29616</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>48566</t>
+          <t>49663</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>64582</t>
+          <t>65261</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>86,11%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>7102</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19682</t>
+          <t>19677</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11118</t>
+          <t>11000</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>11209</t>
+          <t>10530</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>27225</t>
+          <t>26128</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>34,47%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>226963</t>
+          <t>227282</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>260196</t>
+          <t>259495</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>79,44%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>153383</t>
+          <t>153048</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>178952</t>
+          <t>177544</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>389548</t>
+          <t>388400</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>431185</t>
+          <t>429377</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,34%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>67358</t>
+          <t>68059</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>100591</t>
+          <t>100272</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>34709</t>
+          <t>36117</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>60278</t>
+          <t>60613</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>110029</t>
+          <t>111837</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>151666</t>
+          <t>152814</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,24%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2016</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26128</t>
+          <t>26374</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42259</t>
+          <t>41913</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21261</t>
+          <t>22094</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33682</t>
+          <t>33686</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52533</t>
+          <t>52537</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>73318</t>
+          <t>72526</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>72,92%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16318</t>
+          <t>16664</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32449</t>
+          <t>32203</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>7198</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19623</t>
+          <t>18790</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26143</t>
+          <t>26935</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46928</t>
+          <t>46924</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69099</t>
+          <t>68798</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79630</t>
+          <t>79678</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33182</t>
+          <t>32804</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41612</t>
+          <t>41534</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>105750</t>
+          <t>105023</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>119259</t>
+          <t>118947</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>94,79%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3156</t>
+          <t>3108</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13687</t>
+          <t>13988</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1163</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9515</t>
+          <t>9893</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6224</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19733</t>
+          <t>20460</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>16,3%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12820</t>
+          <t>13059</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20346</t>
+          <t>20355</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7239</t>
+          <t>6793</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23565</t>
+          <t>22559</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31347</t>
+          <t>31227</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,51%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>899</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8434</t>
+          <t>8195</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5262</t>
+          <t>5708</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2528</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10190</t>
+          <t>11196</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>33,17%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21425</t>
+          <t>20660</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30154</t>
+          <t>29768</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20098</t>
+          <t>20876</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28098</t>
+          <t>28108</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44536</t>
+          <t>44533</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56463</t>
+          <t>56588</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,69%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2311</t>
+          <t>2697</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11040</t>
+          <t>11805</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1837</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9837</t>
+          <t>9059</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5937</t>
+          <t>5812</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17864</t>
+          <t>17867</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,7 +8606,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7705</t>
+          <t>8113</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11543</t>
+          <t>12307</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19721</t>
+          <t>19754</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,7%</t>
         </is>
       </c>
     </row>
@@ -8869,7 +8869,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7165</t>
+          <t>6757</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3744</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8919,7 +8919,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>887</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9098</t>
+          <t>8334</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>40,37%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6367</t>
+          <t>5803</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15567</t>
+          <t>15466</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5700</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7427</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12647</t>
+          <t>13014</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23906</t>
+          <t>23442</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>78,51%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6867</t>
+          <t>6968</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16067</t>
+          <t>16631</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1727</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5954</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17213</t>
+          <t>16846</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>56,42%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>56034</t>
+          <t>55462</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>70971</t>
+          <t>70637</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43026</t>
+          <t>43818</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>54011</t>
+          <t>54002</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>104822</t>
+          <t>104467</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>122279</t>
+          <t>123425</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>92,09%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7371</t>
+          <t>7705</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22308</t>
+          <t>22880</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1671</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12656</t>
+          <t>11864</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>11745</t>
+          <t>10599</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>29202</t>
+          <t>29557</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,05%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12429</t>
+          <t>12465</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>25782</t>
+          <t>25257</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12395</t>
+          <t>12643</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20399</t>
+          <t>20396</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>28755</t>
+          <t>28497</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>44141</t>
+          <t>44145</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,76%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13492</t>
+          <t>14017</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26845</t>
+          <t>26809</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9005</t>
+          <t>8757</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>16533</t>
+          <t>16529</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>31919</t>
+          <t>32177</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>53,03%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>243733</t>
+          <t>242826</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>277615</t>
+          <t>274945</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>171011</t>
+          <t>172284</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>192299</t>
+          <t>193490</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>423295</t>
+          <t>422810</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>464402</t>
+          <t>463700</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>81,88%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>72386</t>
+          <t>75056</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>106268</t>
+          <t>107175</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>23999</t>
+          <t>22808</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>45287</t>
+          <t>44014</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>101897</t>
+          <t>102599</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>143004</t>
+          <t>143489</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,34%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2023</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores en la espalda en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9979</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19851</t>
+          <t>19937</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>42,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7300</t>
+          <t>7489</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13862</t>
+          <t>14022</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20346</t>
+          <t>20305</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32167</t>
+          <t>32900</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>82,61%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4218</t>
+          <t>4132</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14090</t>
+          <t>13766</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8455</t>
+          <t>8266</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,66%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7657</t>
+          <t>6924</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19478</t>
+          <t>19519</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>49,01%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30479</t>
+          <t>30927</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42866</t>
+          <t>43067</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35719</t>
+          <t>35130</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43749</t>
+          <t>43372</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>70147</t>
+          <t>69807</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84654</t>
+          <t>84415</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,03%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15801</t>
+          <t>15353</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>33,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1694</t>
+          <t>2071</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>10313</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>7308</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21576</t>
+          <t>21916</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,89%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21026</t>
+          <t>21223</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34206</t>
+          <t>34784</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,11%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26432</t>
+          <t>26829</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36730</t>
+          <t>36888</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51891</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68308</t>
+          <t>68518</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,59%</t>
+          <t>71,81%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15289</t>
+          <t>14711</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28469</t>
+          <t>28272</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9196</t>
+          <t>9038</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19494</t>
+          <t>19097</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27114</t>
+          <t>26904</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>43531</t>
+          <t>43673</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,62%</t>
+          <t>45,77%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19239</t>
+          <t>19857</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34115</t>
+          <t>34527</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55395</t>
+          <t>56315</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77091</t>
+          <t>77369</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>81301</t>
+          <t>80305</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>112301</t>
+          <t>109873</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>90,8%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6238</t>
+          <t>5826</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21114</t>
+          <t>20496</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3561</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25257</t>
+          <t>24337</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8704</t>
+          <t>11132</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39704</t>
+          <t>40700</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>33,63%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11933</t>
+          <t>12081</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17026</t>
+          <t>17037</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7124</t>
+          <t>7071</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10546</t>
+          <t>10605</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20806</t>
+          <t>21054</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26673</t>
+          <t>26534</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,31%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>720</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>5676</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>381</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3862</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2209</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7937</t>
+          <t>7689</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>26,75%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16436</t>
+          <t>15918</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25834</t>
+          <t>25529</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18027</t>
+          <t>18018</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25992</t>
+          <t>25873</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>37561</t>
+          <t>37527</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49930</t>
+          <t>49825</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>60,75%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,58%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5782</t>
+          <t>6087</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15180</t>
+          <t>15698</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4223</t>
+          <t>4342</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12188</t>
+          <t>12197</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11901</t>
+          <t>12006</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>24270</t>
+          <t>24304</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,31%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>40564</t>
+          <t>40068</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57728</t>
+          <t>56690</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44510</t>
+          <t>43904</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>58837</t>
+          <t>58180</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>90999</t>
+          <t>89795</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>111913</t>
+          <t>112716</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>78,44%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15450</t>
+          <t>16488</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>32614</t>
+          <t>33110</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11690</t>
+          <t>12347</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>26017</t>
+          <t>26623</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>31792</t>
+          <t>30989</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>52706</t>
+          <t>53910</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>37,51%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>45741</t>
+          <t>46559</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>54821</t>
+          <t>54822</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,7 +13118,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>27705</t>
+          <t>26455</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>47003</t>
+          <t>46731</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>76834</t>
+          <t>76297</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>99634</t>
+          <t>100060</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,77%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1936</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11016</t>
+          <t>10198</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13236,7 +13236,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7707</t>
+          <t>7979</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>27005</t>
+          <t>28255</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>11833</t>
+          <t>11407</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>34633</t>
+          <t>35170</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,55%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>229201</t>
+          <t>229067</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>264426</t>
+          <t>262543</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>256445</t>
+          <t>256929</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>297888</t>
+          <t>297664</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>498342</t>
+          <t>497433</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>553674</t>
+          <t>552447</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>79,64%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>75079</t>
+          <t>76962</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>110304</t>
+          <t>110438</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>56327</t>
+          <t>56551</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>97770</t>
+          <t>97286</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>140046</t>
+          <t>141273</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>195378</t>
+          <t>196287</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,29%</t>
         </is>
       </c>
     </row>
